--- a/cloud_DevOps/Cloud_DevOps_Training_Refined_Upto_15_April.xlsx
+++ b/cloud_DevOps/Cloud_DevOps_Training_Refined_Upto_15_April.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS\DevOps-Bootcamp-30\cloud_DevOps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BCEA67-2F62-4A47-AE0A-85E1D419D3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52BC4EDD-19FE-4627-A0AF-180100340A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -225,14 +225,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -541,7 +540,7 @@
     <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.6640625" customWidth="1"/>
     <col min="3" max="3" width="53.33203125" customWidth="1"/>
-    <col min="4" max="4" width="27.109375" customWidth="1"/>
+    <col min="4" max="4" width="12.77734375" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="59.33203125" customWidth="1"/>
   </cols>
@@ -584,7 +583,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -745,7 +744,6 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C12" s="4"/>
       <c r="E12">
         <f>SUM(E2:E11)</f>
         <v>30</v>
